--- a/AtchisonRegime/Outputs/India/df_regCLI_India.xlsx
+++ b/AtchisonRegime/Outputs/India/df_regCLI_India.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H338"/>
+  <dimension ref="A1:H339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8957,22 +8957,22 @@
         <v>45443</v>
       </c>
       <c r="B328" t="n">
-        <v>100.19</v>
+        <v>100.055</v>
       </c>
       <c r="C328" t="n">
-        <v>100.1266666666667</v>
+        <v>100.0816666666667</v>
       </c>
       <c r="D328" t="n">
-        <v>100.1461111111111</v>
+        <v>100.1423611111111</v>
       </c>
       <c r="E328" t="n">
-        <v>0.4725328576801093</v>
+        <v>0.4727102496865914</v>
       </c>
       <c r="F328" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G328" t="n">
-        <v>0.1269752971138792</v>
+        <v>-0.1586595595287259</v>
       </c>
       <c r="H328" t="b">
         <v>1</v>
@@ -8983,22 +8983,22 @@
         <v>45473</v>
       </c>
       <c r="B329" t="n">
-        <v>100.23</v>
+        <v>100.1191</v>
       </c>
       <c r="C329" t="n">
-        <v>100.1833333333333</v>
+        <v>100.1013666666667</v>
       </c>
       <c r="D329" t="n">
-        <v>100.1333333333333</v>
+        <v>100.1265027777778</v>
       </c>
       <c r="E329" t="n">
-        <v>0.4635391800361676</v>
+        <v>0.4632957558845832</v>
       </c>
       <c r="F329" t="b">
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>0.08629259774089702</v>
+        <v>0.1383565447898576</v>
       </c>
       <c r="H329" t="b">
         <v>1</v>
@@ -9009,22 +9009,22 @@
         <v>45504</v>
       </c>
       <c r="B330" t="n">
-        <v>100.26</v>
+        <v>100.1711</v>
       </c>
       <c r="C330" t="n">
-        <v>100.2266666666667</v>
+        <v>100.1150666666667</v>
       </c>
       <c r="D330" t="n">
-        <v>100.12</v>
+        <v>100.1107</v>
       </c>
       <c r="E330" t="n">
-        <v>0.4523588967054864</v>
+        <v>0.4513194427770718</v>
       </c>
       <c r="F330" t="b">
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>0.06631902283450167</v>
+        <v>0.1152177262296182</v>
       </c>
       <c r="H330" t="b">
         <v>1</v>
@@ -9035,22 +9035,22 @@
         <v>45535</v>
       </c>
       <c r="B331" t="n">
-        <v>100.28</v>
+        <v>100.2118</v>
       </c>
       <c r="C331" t="n">
-        <v>100.2566666666667</v>
+        <v>100.1673333333333</v>
       </c>
       <c r="D331" t="n">
-        <v>100.1061111111111</v>
+        <v>100.0949166666667</v>
       </c>
       <c r="E331" t="n">
-        <v>0.4389941605715377</v>
+        <v>0.4369509292488873</v>
       </c>
       <c r="F331" t="b">
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.04555869256656515</v>
+        <v>0.09314547075106079</v>
       </c>
       <c r="H331" t="b">
         <v>1</v>
@@ -9061,22 +9061,22 @@
         <v>45565</v>
       </c>
       <c r="B332" t="n">
-        <v>100.28</v>
+        <v>100.2425</v>
       </c>
       <c r="C332" t="n">
-        <v>100.2733333333333</v>
+        <v>100.2084666666667</v>
       </c>
       <c r="D332" t="n">
-        <v>100.0913888888889</v>
+        <v>100.0791527777778</v>
       </c>
       <c r="E332" t="n">
-        <v>0.4233212409222005</v>
+        <v>0.4203367585205127</v>
       </c>
       <c r="F332" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G332" t="n">
-        <v>0</v>
+        <v>0.0730366768494552</v>
       </c>
       <c r="H332" t="b">
         <v>1</v>
@@ -9087,22 +9087,22 @@
         <v>45596</v>
       </c>
       <c r="B333" t="n">
-        <v>100.26</v>
+        <v>100.2666</v>
       </c>
       <c r="C333" t="n">
-        <v>100.2733333333333</v>
+        <v>100.2403</v>
       </c>
       <c r="D333" t="n">
-        <v>100.0758333333333</v>
+        <v>100.0637805555556</v>
       </c>
       <c r="E333" t="n">
-        <v>0.4057048540151704</v>
+        <v>0.4021968081279317</v>
       </c>
       <c r="F333" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>-0.04929692066057501</v>
+        <v>0.05992091312749612</v>
       </c>
       <c r="H333" t="b">
         <v>1</v>
@@ -9113,25 +9113,25 @@
         <v>45626</v>
       </c>
       <c r="B334" t="n">
-        <v>100.24</v>
+        <v>100.2873</v>
       </c>
       <c r="C334" t="n">
-        <v>100.26</v>
+        <v>100.2654666666667</v>
       </c>
       <c r="D334" t="n">
-        <v>100.0597222222222</v>
+        <v>100.0489833333333</v>
       </c>
       <c r="E334" t="n">
-        <v>0.386363900347987</v>
+        <v>0.3829170051815244</v>
       </c>
       <c r="F334" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G334" t="n">
-        <v>-0.05176467051398125</v>
+        <v>0.05405871173099788</v>
       </c>
       <c r="H334" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -9139,25 +9139,25 @@
         <v>45657</v>
       </c>
       <c r="B335" t="n">
-        <v>100.21</v>
+        <v>100.3066</v>
       </c>
       <c r="C335" t="n">
-        <v>100.2366666666667</v>
+        <v>100.2868333333333</v>
       </c>
       <c r="D335" t="n">
-        <v>100.0430555555556</v>
+        <v>100.035</v>
       </c>
       <c r="E335" t="n">
-        <v>0.3654493863290825</v>
+        <v>0.3630061361150653</v>
       </c>
       <c r="F335" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>-0.08209071111419658</v>
+        <v>0.05316714534512307</v>
       </c>
       <c r="H335" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -9165,25 +9165,25 @@
         <v>45688</v>
       </c>
       <c r="B336" t="n">
-        <v>100.19</v>
+        <v>100.3273</v>
       </c>
       <c r="C336" t="n">
-        <v>100.2133333333333</v>
+        <v>100.3070666666667</v>
       </c>
       <c r="D336" t="n">
-        <v>100.0266666666667</v>
+        <v>100.022425</v>
       </c>
       <c r="E336" t="n">
-        <v>0.3440597954675832</v>
+        <v>0.3437936468914241</v>
       </c>
       <c r="F336" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>-0.05812943059160887</v>
+        <v>0.06021053671922057</v>
       </c>
       <c r="H336" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -9191,25 +9191,25 @@
         <v>45716</v>
       </c>
       <c r="B337" t="n">
-        <v>100.16</v>
+        <v>100.3508</v>
       </c>
       <c r="C337" t="n">
-        <v>100.1866666666667</v>
+        <v>100.3282333333333</v>
       </c>
       <c r="D337" t="n">
-        <v>100.0108333333333</v>
+        <v>100.0118916666667</v>
       </c>
       <c r="E337" t="n">
-        <v>0.323254654148439</v>
+        <v>0.3268886235621167</v>
       </c>
       <c r="F337" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G337" t="n">
-        <v>-0.09280608837336365</v>
+        <v>0.07188992918729449</v>
       </c>
       <c r="H337" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
@@ -9217,25 +9217,51 @@
         <v>45747</v>
       </c>
       <c r="B338" t="n">
-        <v>100.1</v>
+        <v>100.3774</v>
       </c>
       <c r="C338" t="n">
-        <v>100.15</v>
+        <v>100.3518333333333</v>
       </c>
       <c r="D338" t="n">
-        <v>99.995</v>
+        <v>100.0037638888889</v>
       </c>
       <c r="E338" t="n">
-        <v>0.3033950748259275</v>
+        <v>0.3134179137490079</v>
       </c>
       <c r="F338" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>-0.1977619446671215</v>
+        <v>0.08487070723497196</v>
       </c>
       <c r="H338" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B339" t="n">
+        <v>100.4062</v>
+      </c>
+      <c r="C339" t="n">
+        <v>100.3781333333333</v>
+      </c>
+      <c r="D339" t="n">
+        <v>99.99838055555556</v>
+      </c>
+      <c r="E339" t="n">
+        <v>0.304419430410022</v>
+      </c>
+      <c r="F339" t="b">
+        <v>1</v>
+      </c>
+      <c r="G339" t="n">
+        <v>0.09460631327380538</v>
+      </c>
+      <c r="H339" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
